--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125338077</v>
+        <v>125338104</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547122</v>
+        <v>547070</v>
       </c>
       <c r="R4" t="n">
-        <v>7151950</v>
+        <v>7151921</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färskt hack vid granbas</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125338074</v>
+        <v>125338099</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,37 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547325</v>
+        <v>547290</v>
       </c>
       <c r="R5" t="n">
-        <v>7152098</v>
+        <v>7152033</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1110,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125338082</v>
+        <v>125338102</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,37 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547586</v>
+        <v>547134</v>
       </c>
       <c r="R7" t="n">
-        <v>7152433</v>
+        <v>7151943</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1347,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,12 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe och låga</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1344,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1390,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125338104</v>
+        <v>125338091</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,34 +1378,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547070</v>
+        <v>547078</v>
       </c>
       <c r="R8" t="n">
-        <v>7151921</v>
+        <v>7151964</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1465,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,8 +1459,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1502,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125338094</v>
+        <v>125338071</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,34 +1509,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547755</v>
+        <v>547313</v>
       </c>
       <c r="R9" t="n">
-        <v>7152493</v>
+        <v>7152071</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1577,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1731,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125338069</v>
+        <v>125338074</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,39 +1748,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547781</v>
+        <v>547325</v>
       </c>
       <c r="R11" t="n">
-        <v>7152531</v>
+        <v>7152098</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,12 +1820,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,6 +1834,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125338088</v>
+        <v>125338100</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,21 +1869,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547454</v>
+        <v>547271</v>
       </c>
       <c r="R12" t="n">
-        <v>7152339</v>
+        <v>7152000</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,12 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125339276</v>
+        <v>125338093</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,21 +1981,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2010,10 +2005,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547306</v>
+        <v>547773</v>
       </c>
       <c r="R13" t="n">
-        <v>7152046</v>
+        <v>7152591</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2045,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,12 +2050,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338091</v>
+        <v>125338088</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,37 +2093,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547078</v>
+        <v>547454</v>
       </c>
       <c r="R14" t="n">
-        <v>7151964</v>
+        <v>7152339</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2165,7 +2152,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2162,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,24 +2176,8 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2218,7 +2194,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338100</v>
+        <v>125338096</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2258,10 +2234,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547271</v>
+        <v>547447</v>
       </c>
       <c r="R15" t="n">
-        <v>7152000</v>
+        <v>7152303</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2293,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2330,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125338071</v>
+        <v>125338094</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,39 +2322,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547313</v>
+        <v>547755</v>
       </c>
       <c r="R16" t="n">
-        <v>7152071</v>
+        <v>7152493</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2410,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,12 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125338096</v>
+        <v>125338079</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,25 +2430,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2492,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547447</v>
+        <v>547621</v>
       </c>
       <c r="R17" t="n">
-        <v>7152303</v>
+        <v>7152312</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2527,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2537,7 +2503,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg naturvårdsträd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2564,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338099</v>
+        <v>125338082</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,34 +2551,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547290</v>
+        <v>547586</v>
       </c>
       <c r="R18" t="n">
-        <v>7152033</v>
+        <v>7152433</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2639,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,7 +2623,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe och låga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,6 +2637,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2676,10 +2656,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125338102</v>
+        <v>125339276</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,21 +2672,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2716,10 +2696,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547134</v>
+        <v>547306</v>
       </c>
       <c r="R19" t="n">
-        <v>7151943</v>
+        <v>7152046</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2751,7 +2731,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2761,7 +2741,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2788,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125338079</v>
+        <v>125338077</v>
       </c>
       <c r="B20" t="n">
-        <v>79927</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,38 +2785,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547621</v>
+        <v>547122</v>
       </c>
       <c r="R20" t="n">
-        <v>7152312</v>
+        <v>7151950</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2863,7 +2853,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2873,12 +2863,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gammal levande sälg naturvårdsträd</t>
+          <t>Färskt hack vid granbas</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,10 +2895,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125338093</v>
+        <v>125338069</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2921,34 +2911,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547773</v>
+        <v>547781</v>
       </c>
       <c r="R21" t="n">
-        <v>7152591</v>
+        <v>7152531</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2980,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2990,7 +2985,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125338105</v>
+        <v>125338091</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547274</v>
+        <v>547078</v>
       </c>
       <c r="R2" t="n">
-        <v>7152036</v>
+        <v>7151964</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,8 +772,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125338084</v>
+        <v>125339276</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +822,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547534</v>
+        <v>547306</v>
       </c>
       <c r="R3" t="n">
-        <v>7152356</v>
+        <v>7152046</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -904,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125338104</v>
+        <v>125338094</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -944,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547070</v>
+        <v>547755</v>
       </c>
       <c r="R4" t="n">
-        <v>7151921</v>
+        <v>7152493</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125338099</v>
+        <v>125338071</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1051,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547290</v>
+        <v>547313</v>
       </c>
       <c r="R5" t="n">
-        <v>7152033</v>
+        <v>7152071</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125338070</v>
+        <v>125338096</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1173,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547761</v>
+        <v>547447</v>
       </c>
       <c r="R6" t="n">
-        <v>7152494</v>
+        <v>7152303</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1208,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125338102</v>
+        <v>125338069</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1285,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547134</v>
+        <v>547781</v>
       </c>
       <c r="R7" t="n">
-        <v>7151943</v>
+        <v>7152531</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1325,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1359,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125338091</v>
+        <v>125338074</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547078</v>
+        <v>547325</v>
       </c>
       <c r="R8" t="n">
-        <v>7151964</v>
+        <v>7152098</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1440,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1479,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,21 +1496,6 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1493,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125338071</v>
+        <v>125338102</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,39 +1528,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547313</v>
+        <v>547134</v>
       </c>
       <c r="R9" t="n">
-        <v>7152071</v>
+        <v>7151943</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1573,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125338085</v>
+        <v>125338100</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,21 +1640,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547489</v>
+        <v>547271</v>
       </c>
       <c r="R10" t="n">
-        <v>7152341</v>
+        <v>7152000</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1690,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,12 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,7 +1736,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125338074</v>
+        <v>125338088</v>
       </c>
       <c r="B11" t="n">
         <v>78547</v>
@@ -1766,19 +1770,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547325</v>
+        <v>547454</v>
       </c>
       <c r="R11" t="n">
-        <v>7152098</v>
+        <v>7152339</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1810,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,7 +1821,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1834,7 +1835,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125338100</v>
+        <v>125338079</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,25 +1865,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547271</v>
+        <v>547621</v>
       </c>
       <c r="R12" t="n">
-        <v>7152000</v>
+        <v>7152312</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,7 +1938,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg naturvårdsträd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125338093</v>
+        <v>125338070</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,34 +1986,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547773</v>
+        <v>547761</v>
       </c>
       <c r="R13" t="n">
-        <v>7152591</v>
+        <v>7152494</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2040,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2050,7 +2060,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,7 +2092,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338088</v>
+        <v>125338084</v>
       </c>
       <c r="B14" t="n">
         <v>78547</v>
@@ -2117,10 +2132,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547454</v>
+        <v>547534</v>
       </c>
       <c r="R14" t="n">
-        <v>7152339</v>
+        <v>7152356</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2152,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2162,7 +2177,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2194,7 +2209,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338096</v>
+        <v>125338105</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2234,10 +2249,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547447</v>
+        <v>547274</v>
       </c>
       <c r="R15" t="n">
-        <v>7152303</v>
+        <v>7152036</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2269,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,7 +2321,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125338094</v>
+        <v>125338093</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2346,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547755</v>
+        <v>547773</v>
       </c>
       <c r="R16" t="n">
-        <v>7152493</v>
+        <v>7152591</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2381,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2406,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125338079</v>
+        <v>125338099</v>
       </c>
       <c r="B17" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,25 +2445,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2473,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547621</v>
+        <v>547290</v>
       </c>
       <c r="R17" t="n">
-        <v>7152312</v>
+        <v>7152033</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2493,7 +2508,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,12 +2518,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg naturvårdsträd</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2535,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338082</v>
+        <v>125338077</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2551,37 +2561,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547586</v>
+        <v>547122</v>
       </c>
       <c r="R18" t="n">
-        <v>7152433</v>
+        <v>7151950</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2613,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,12 +2635,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe och låga</t>
+          <t>Färskt hack vid granbas</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,7 +2649,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2656,7 +2667,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125339276</v>
+        <v>125338082</v>
       </c>
       <c r="B19" t="n">
         <v>78546</v>
@@ -2690,16 +2701,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547306</v>
+        <v>547586</v>
       </c>
       <c r="R19" t="n">
-        <v>7152046</v>
+        <v>7152433</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2731,7 +2745,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2741,12 +2755,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe</t>
+          <t>Brandskadad stubbe och låga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,6 +2769,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2773,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125338077</v>
+        <v>125338104</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2789,39 +2804,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547122</v>
+        <v>547070</v>
       </c>
       <c r="R20" t="n">
-        <v>7151950</v>
+        <v>7151921</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2853,7 +2863,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2863,12 +2873,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färskt hack vid granbas</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2895,10 +2900,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125338069</v>
+        <v>125338085</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2911,39 +2916,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547781</v>
+        <v>547489</v>
       </c>
       <c r="R21" t="n">
-        <v>7152531</v>
+        <v>7152341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125338091</v>
+        <v>125338100</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547078</v>
+        <v>547271</v>
       </c>
       <c r="R2" t="n">
-        <v>7151964</v>
+        <v>7152000</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,24 +769,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -809,7 +790,7 @@
         <v>125339276</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -923,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125338094</v>
+        <v>125338069</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547755</v>
+        <v>547781</v>
       </c>
       <c r="R4" t="n">
-        <v>7152493</v>
+        <v>7152531</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125338071</v>
+        <v>125338102</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547313</v>
+        <v>547134</v>
       </c>
       <c r="R5" t="n">
-        <v>7152071</v>
+        <v>7151943</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1115,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125338096</v>
+        <v>125338070</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547447</v>
+        <v>547761</v>
       </c>
       <c r="R6" t="n">
-        <v>7152303</v>
+        <v>7152494</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1232,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125338069</v>
+        <v>125338105</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,39 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547781</v>
+        <v>547274</v>
       </c>
       <c r="R7" t="n">
-        <v>7152531</v>
+        <v>7152036</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1349,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125338074</v>
+        <v>125338096</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,37 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547325</v>
+        <v>547447</v>
       </c>
       <c r="R8" t="n">
-        <v>7152098</v>
+        <v>7152303</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1469,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,7 +1466,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1512,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125338102</v>
+        <v>125338093</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547134</v>
+        <v>547773</v>
       </c>
       <c r="R9" t="n">
-        <v>7151943</v>
+        <v>7152591</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1587,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125338100</v>
+        <v>125338077</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,34 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547271</v>
+        <v>547122</v>
       </c>
       <c r="R10" t="n">
-        <v>7152000</v>
+        <v>7151950</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1699,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1686,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färskt hack vid granbas</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125338088</v>
+        <v>125338104</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,21 +1734,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1776,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547454</v>
+        <v>547070</v>
       </c>
       <c r="R11" t="n">
-        <v>7152339</v>
+        <v>7151921</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,12 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125338079</v>
+        <v>125338094</v>
       </c>
       <c r="B12" t="n">
-        <v>79927</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,25 +1842,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1893,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547621</v>
+        <v>547755</v>
       </c>
       <c r="R12" t="n">
-        <v>7152312</v>
+        <v>7152493</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1928,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,12 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg naturvårdsträd</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125338070</v>
+        <v>125338099</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,39 +1958,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547761</v>
+        <v>547290</v>
       </c>
       <c r="R13" t="n">
-        <v>7152494</v>
+        <v>7152033</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2050,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,12 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338084</v>
+        <v>125338088</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2132,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547534</v>
+        <v>547454</v>
       </c>
       <c r="R14" t="n">
-        <v>7152356</v>
+        <v>7152339</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2167,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2209,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338105</v>
+        <v>125338091</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,34 +2187,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547274</v>
+        <v>547078</v>
       </c>
       <c r="R15" t="n">
-        <v>7152036</v>
+        <v>7151964</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2284,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,8 +2268,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2321,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125338093</v>
+        <v>125338085</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78684</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,21 +2318,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2361,10 +2342,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547773</v>
+        <v>547489</v>
       </c>
       <c r="R16" t="n">
-        <v>7152591</v>
+        <v>7152341</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2396,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,7 +2387,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125338099</v>
+        <v>125338071</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,34 +2435,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547290</v>
+        <v>547313</v>
       </c>
       <c r="R17" t="n">
-        <v>7152033</v>
+        <v>7152071</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2508,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2518,7 +2509,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338077</v>
+        <v>125338074</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>78684</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2561,39 +2557,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547122</v>
+        <v>547325</v>
       </c>
       <c r="R18" t="n">
-        <v>7151950</v>
+        <v>7152098</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2625,7 +2619,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,12 +2629,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färskt hack vid granbas</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,6 +2643,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2667,10 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125338082</v>
+        <v>125338084</v>
       </c>
       <c r="B19" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2683,37 +2678,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547586</v>
+        <v>547534</v>
       </c>
       <c r="R19" t="n">
-        <v>7152433</v>
+        <v>7152356</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2745,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2755,12 +2747,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe och låga</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,7 +2761,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2788,10 +2779,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125338104</v>
+        <v>125338082</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,34 +2795,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547070</v>
+        <v>547586</v>
       </c>
       <c r="R20" t="n">
-        <v>7151921</v>
+        <v>7152433</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2863,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2873,7 +2867,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe och låga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,6 +2881,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125338085</v>
+        <v>125338079</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>80064</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,25 +2912,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547489</v>
+        <v>547621</v>
       </c>
       <c r="R21" t="n">
-        <v>7152341</v>
+        <v>7152312</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe</t>
+          <t>Gammal levande sälg naturvårdsträd</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125338100</v>
+        <v>125338105</v>
       </c>
       <c r="B2" t="n">
         <v>78947</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547271</v>
+        <v>547274</v>
       </c>
       <c r="R2" t="n">
-        <v>7152000</v>
+        <v>7152036</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125339276</v>
+        <v>125338088</v>
       </c>
       <c r="B3" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547306</v>
+        <v>547454</v>
       </c>
       <c r="R3" t="n">
-        <v>7152046</v>
+        <v>7152339</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125338069</v>
+        <v>125338074</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>78684</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547781</v>
+        <v>547325</v>
       </c>
       <c r="R4" t="n">
-        <v>7152531</v>
+        <v>7152098</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -984,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +992,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,6 +1006,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1026,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125338102</v>
+        <v>125338079</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>80064</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1037,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547134</v>
+        <v>547621</v>
       </c>
       <c r="R5" t="n">
-        <v>7151943</v>
+        <v>7152312</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1101,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg naturvårdsträd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125338070</v>
+        <v>125338104</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547761</v>
+        <v>547070</v>
       </c>
       <c r="R6" t="n">
-        <v>7152494</v>
+        <v>7151921</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1218,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125338105</v>
+        <v>125338071</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1270,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547274</v>
+        <v>547313</v>
       </c>
       <c r="R7" t="n">
-        <v>7152036</v>
+        <v>7152071</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1335,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125338096</v>
+        <v>125338070</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1392,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547447</v>
+        <v>547761</v>
       </c>
       <c r="R8" t="n">
-        <v>7152303</v>
+        <v>7152494</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1447,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125338093</v>
+        <v>125338091</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1514,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547773</v>
+        <v>547078</v>
       </c>
       <c r="R9" t="n">
-        <v>7152591</v>
+        <v>7151964</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1559,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,8 +1595,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125338077</v>
+        <v>125338082</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>78683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1645,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547122</v>
+        <v>547586</v>
       </c>
       <c r="R10" t="n">
-        <v>7151950</v>
+        <v>7152433</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,7 +1707,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,12 +1717,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färskt hack vid granbas</t>
+          <t>Brandskadad stubbe och låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,6 +1731,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1718,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125338104</v>
+        <v>125338069</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,34 +1766,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547070</v>
+        <v>547781</v>
       </c>
       <c r="R11" t="n">
-        <v>7151921</v>
+        <v>7152531</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1793,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1840,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,7 +1872,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125338094</v>
+        <v>125338102</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
@@ -1870,10 +1912,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547755</v>
+        <v>547134</v>
       </c>
       <c r="R12" t="n">
-        <v>7152493</v>
+        <v>7151943</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1905,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125338099</v>
+        <v>125338084</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,21 +2000,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547290</v>
+        <v>547534</v>
       </c>
       <c r="R13" t="n">
-        <v>7152033</v>
+        <v>7152356</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2017,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2069,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2101,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338088</v>
+        <v>125339276</v>
       </c>
       <c r="B14" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,21 +2117,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2141,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547454</v>
+        <v>547306</v>
       </c>
       <c r="R14" t="n">
-        <v>7152339</v>
+        <v>7152046</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2129,7 +2176,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2171,10 +2218,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338091</v>
+        <v>125338099</v>
       </c>
       <c r="B15" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,37 +2234,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547078</v>
+        <v>547290</v>
       </c>
       <c r="R15" t="n">
-        <v>7151964</v>
+        <v>7152033</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2249,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,24 +2312,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2302,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125338085</v>
+        <v>125338093</v>
       </c>
       <c r="B16" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,21 +2346,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2342,10 +2370,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547489</v>
+        <v>547773</v>
       </c>
       <c r="R16" t="n">
-        <v>7152341</v>
+        <v>7152591</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2377,7 +2405,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,12 +2415,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125338071</v>
+        <v>125338077</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2435,16 +2458,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2464,10 +2487,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547313</v>
+        <v>547122</v>
       </c>
       <c r="R17" t="n">
-        <v>7152071</v>
+        <v>7151950</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2499,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,12 +2532,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färskt hack vid granbas</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2564,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338074</v>
+        <v>125338100</v>
       </c>
       <c r="B18" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2557,37 +2580,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547325</v>
+        <v>547271</v>
       </c>
       <c r="R18" t="n">
-        <v>7152098</v>
+        <v>7152000</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2619,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2629,12 +2649,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,7 +2658,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2662,7 +2676,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125338084</v>
+        <v>125338085</v>
       </c>
       <c r="B19" t="n">
         <v>78684</v>
@@ -2702,10 +2716,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547534</v>
+        <v>547489</v>
       </c>
       <c r="R19" t="n">
-        <v>7152356</v>
+        <v>7152341</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2737,7 +2751,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2761,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2779,10 +2793,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125338082</v>
+        <v>125338094</v>
       </c>
       <c r="B20" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,37 +2809,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547586</v>
+        <v>547755</v>
       </c>
       <c r="R20" t="n">
-        <v>7152433</v>
+        <v>7152493</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2857,7 +2868,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2867,12 +2878,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe och låga</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2881,7 +2887,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2900,10 +2905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125338079</v>
+        <v>125338096</v>
       </c>
       <c r="B21" t="n">
-        <v>80064</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,25 +2917,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2940,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547621</v>
+        <v>547447</v>
       </c>
       <c r="R21" t="n">
-        <v>7152312</v>
+        <v>7152303</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2975,7 +2980,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,12 +2990,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg naturvårdsträd</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -2564,10 +2564,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338100</v>
+        <v>125338085</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547271</v>
+        <v>547489</v>
       </c>
       <c r="R18" t="n">
-        <v>7152000</v>
+        <v>7152341</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,7 +2649,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125338085</v>
+        <v>125338100</v>
       </c>
       <c r="B19" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2716,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547489</v>
+        <v>547271</v>
       </c>
       <c r="R19" t="n">
-        <v>7152341</v>
+        <v>7152000</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2751,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2761,12 +2766,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125338105</v>
+        <v>125338077</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547274</v>
+        <v>547122</v>
       </c>
       <c r="R2" t="n">
-        <v>7152036</v>
+        <v>7151950</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färskt hack vid granbas</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125338088</v>
+        <v>125338105</v>
       </c>
       <c r="B3" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547454</v>
+        <v>547274</v>
       </c>
       <c r="R3" t="n">
-        <v>7152339</v>
+        <v>7152036</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125338074</v>
+        <v>125338102</v>
       </c>
       <c r="B4" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,37 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547325</v>
+        <v>547134</v>
       </c>
       <c r="R4" t="n">
-        <v>7152098</v>
+        <v>7151943</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -982,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +988,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,37 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125338079</v>
+        <v>125338088</v>
       </c>
       <c r="B5" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547621</v>
+        <v>547454</v>
       </c>
       <c r="R5" t="n">
-        <v>7152312</v>
+        <v>7152339</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1100,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gammal levande sälg naturvårdsträd</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,37 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125338104</v>
+        <v>125338079</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547070</v>
+        <v>547621</v>
       </c>
       <c r="R6" t="n">
-        <v>7151921</v>
+        <v>7152312</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1217,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg naturvårdsträd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125338071</v>
+        <v>125338100</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,39 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547313</v>
+        <v>547271</v>
       </c>
       <c r="R7" t="n">
-        <v>7152071</v>
+        <v>7152000</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1334,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,15 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125338070</v>
+        <v>125338104</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,39 +1348,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547761</v>
+        <v>547070</v>
       </c>
       <c r="R8" t="n">
-        <v>7152494</v>
+        <v>7151921</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1456,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,15 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125338091</v>
+        <v>125338069</v>
       </c>
       <c r="B9" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,37 +1455,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547078</v>
+        <v>547781</v>
       </c>
       <c r="R9" t="n">
-        <v>7151964</v>
+        <v>7152531</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1576,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1529,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,24 +1543,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1629,15 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125338082</v>
+        <v>125338071</v>
       </c>
       <c r="B10" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,37 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547586</v>
+        <v>547313</v>
       </c>
       <c r="R10" t="n">
-        <v>7152433</v>
+        <v>7152071</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1707,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1717,12 +1646,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe och låga</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1660,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1750,15 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125338069</v>
+        <v>125338082</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,39 +1689,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547781</v>
+        <v>547586</v>
       </c>
       <c r="R11" t="n">
-        <v>7152531</v>
+        <v>7152433</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1830,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,12 +1761,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Brandskadad stubbe och låga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,6 +1775,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1872,15 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125338102</v>
+        <v>125338094</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547134</v>
+        <v>547755</v>
       </c>
       <c r="R12" t="n">
-        <v>7151943</v>
+        <v>7152493</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1947,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1957,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,15 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125338084</v>
+        <v>125338099</v>
       </c>
       <c r="B13" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547534</v>
+        <v>547290</v>
       </c>
       <c r="R13" t="n">
-        <v>7152356</v>
+        <v>7152033</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2059,7 +1971,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,12 +1981,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,15 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125339276</v>
+        <v>125338085</v>
       </c>
       <c r="B14" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,21 +2019,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2141,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547306</v>
+        <v>547489</v>
       </c>
       <c r="R14" t="n">
-        <v>7152046</v>
+        <v>7152341</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2176,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2186,7 +2088,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2218,15 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338099</v>
+        <v>125338096</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547290</v>
+        <v>547447</v>
       </c>
       <c r="R15" t="n">
-        <v>7152033</v>
+        <v>7152303</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2293,7 +2190,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,7 +2200,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2330,15 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125338093</v>
+        <v>125338070</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,34 +2238,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547773</v>
+        <v>547761</v>
       </c>
       <c r="R16" t="n">
-        <v>7152591</v>
+        <v>7152494</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2405,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2415,7 +2312,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,15 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125338077</v>
+        <v>125338074</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,39 +2355,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547122</v>
+        <v>547325</v>
       </c>
       <c r="R17" t="n">
-        <v>7151950</v>
+        <v>7152098</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2522,7 +2417,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,12 +2427,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färskt hack vid granbas</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,6 +2441,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2564,15 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338085</v>
+        <v>125338084</v>
       </c>
       <c r="B18" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547489</v>
+        <v>547534</v>
       </c>
       <c r="R18" t="n">
-        <v>7152341</v>
+        <v>7152356</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2639,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2681,15 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125338100</v>
+        <v>125339276</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,21 +2583,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547271</v>
+        <v>547306</v>
       </c>
       <c r="R19" t="n">
-        <v>7152000</v>
+        <v>7152046</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2756,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2652,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,15 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125338094</v>
+        <v>125338093</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,10 +2719,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547755</v>
+        <v>547773</v>
       </c>
       <c r="R20" t="n">
-        <v>7152493</v>
+        <v>7152591</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2868,7 +2754,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2878,7 +2764,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,15 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125338096</v>
+        <v>125338091</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,34 +2802,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547447</v>
+        <v>547078</v>
       </c>
       <c r="R21" t="n">
-        <v>7152303</v>
+        <v>7151964</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2980,7 +2864,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2990,7 +2874,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2999,8 +2883,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338085</v>
+        <v>125338096</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,21 +2019,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547489</v>
+        <v>547447</v>
       </c>
       <c r="R14" t="n">
-        <v>7152341</v>
+        <v>7152303</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,12 +2088,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338096</v>
+        <v>125338085</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2126,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547447</v>
+        <v>547489</v>
       </c>
       <c r="R15" t="n">
-        <v>7152303</v>
+        <v>7152341</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2190,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2200,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -2794,7 +2794,7 @@
         <v>125338091</v>
       </c>
       <c r="B21" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338096</v>
+        <v>125338085</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,21 +2019,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547447</v>
+        <v>547489</v>
       </c>
       <c r="R14" t="n">
-        <v>7152303</v>
+        <v>7152341</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,7 +2088,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338085</v>
+        <v>125338096</v>
       </c>
       <c r="B15" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547489</v>
+        <v>547447</v>
       </c>
       <c r="R15" t="n">
-        <v>7152341</v>
+        <v>7152303</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2185,7 +2190,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2200,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125338105</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125338102</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>125338088</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>125338079</v>
       </c>
       <c r="B6" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>125338100</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>125338104</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>125338082</v>
       </c>
       <c r="B11" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>125338094</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125338099</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338085</v>
+        <v>125338096</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,21 +2019,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547489</v>
+        <v>547447</v>
       </c>
       <c r="R14" t="n">
-        <v>7152341</v>
+        <v>7152303</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,12 +2088,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338096</v>
+        <v>125338085</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2126,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547447</v>
+        <v>547489</v>
       </c>
       <c r="R15" t="n">
-        <v>7152303</v>
+        <v>7152341</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2190,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2200,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125338070</v>
+        <v>125338074</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>78727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,39 +2238,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547761</v>
+        <v>547325</v>
       </c>
       <c r="R16" t="n">
-        <v>7152494</v>
+        <v>7152098</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2302,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,12 +2310,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,6 +2324,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2344,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125338074</v>
+        <v>125338084</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,19 +2372,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547325</v>
+        <v>547534</v>
       </c>
       <c r="R17" t="n">
-        <v>7152098</v>
+        <v>7152356</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2417,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2427,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2441,7 +2437,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2460,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338084</v>
+        <v>125338070</v>
       </c>
       <c r="B18" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,34 +2466,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547534</v>
+        <v>547761</v>
       </c>
       <c r="R18" t="n">
-        <v>7152356</v>
+        <v>7152494</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,7 +2575,7 @@
         <v>125339276</v>
       </c>
       <c r="B19" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>125338093</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>125338091</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338096</v>
+        <v>125338085</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,21 +2019,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547447</v>
+        <v>547489</v>
       </c>
       <c r="R14" t="n">
-        <v>7152303</v>
+        <v>7152341</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,7 +2088,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338085</v>
+        <v>125338096</v>
       </c>
       <c r="B15" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547489</v>
+        <v>547447</v>
       </c>
       <c r="R15" t="n">
-        <v>7152341</v>
+        <v>7152303</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2185,7 +2190,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2200,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125338074</v>
+        <v>125338070</v>
       </c>
       <c r="B16" t="n">
-        <v>78727</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,37 +2238,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547325</v>
+        <v>547761</v>
       </c>
       <c r="R16" t="n">
-        <v>7152098</v>
+        <v>7152494</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2300,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,12 +2312,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,7 +2326,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2343,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125338084</v>
+        <v>125338074</v>
       </c>
       <c r="B17" t="n">
         <v>78727</v>
@@ -2372,16 +2373,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547534</v>
+        <v>547325</v>
       </c>
       <c r="R17" t="n">
-        <v>7152356</v>
+        <v>7152098</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2413,7 +2417,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2427,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2437,6 +2441,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2455,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338070</v>
+        <v>125338084</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>78727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,39 +2471,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547761</v>
+        <v>547534</v>
       </c>
       <c r="R18" t="n">
-        <v>7152494</v>
+        <v>7152356</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125338105</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125338102</v>
+        <v>125338088</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547134</v>
+        <v>547454</v>
       </c>
       <c r="R4" t="n">
-        <v>7151943</v>
+        <v>7152339</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125338088</v>
+        <v>125338102</v>
       </c>
       <c r="B5" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547454</v>
+        <v>547134</v>
       </c>
       <c r="R5" t="n">
-        <v>7152339</v>
+        <v>7151943</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1121,7 @@
         <v>125338079</v>
       </c>
       <c r="B6" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>125338100</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>125338104</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125338071</v>
+        <v>125338082</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1572,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547313</v>
+        <v>547586</v>
       </c>
       <c r="R10" t="n">
-        <v>7152071</v>
+        <v>7152433</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1636,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,12 +1644,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Brandskadad stubbe och låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,6 +1658,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1678,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125338082</v>
+        <v>125338071</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,37 +1688,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547586</v>
+        <v>547313</v>
       </c>
       <c r="R11" t="n">
-        <v>7152433</v>
+        <v>7152071</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1751,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,12 +1762,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe och låga</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,7 +1776,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>125338094</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125338099</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>125338085</v>
       </c>
       <c r="B14" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>125338096</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>125338074</v>
       </c>
       <c r="B17" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>125338084</v>
       </c>
       <c r="B18" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>125339276</v>
       </c>
       <c r="B19" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>125338093</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>125338091</v>
       </c>
       <c r="B21" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2915,6 +2915,853 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126612645</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hålbergsvägen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>547244</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7152003</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Synobs. 1 Födosökande</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126612642</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hålbergsvägen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>547118</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7151917</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granstubbe</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126612643</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hålbergsvägen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>547814</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7152348</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126612647</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hålbergsvägen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>547168</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7151946</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Synobs. 2 st födosökande</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126612648</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hålbergsvägen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>547122</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7151913</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126612649</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hålbergsvägen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>547811</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7152358</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 födosökande</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126612644</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hålbergsvägen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>547312</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7152064</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>126612642</v>
       </c>
       <c r="B23" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>126612642</v>
       </c>
       <c r="B23" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -3041,7 +3041,7 @@
         <v>126612642</v>
       </c>
       <c r="B23" t="n">
-        <v>91321</v>
+        <v>91315</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125338077</v>
+        <v>126612642</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547122</v>
+        <v>547118</v>
       </c>
       <c r="R2" t="n">
-        <v>7151950</v>
+        <v>7151917</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färskt hack vid granbas</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,14 +802,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125338105</v>
+        <v>125338093</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547274</v>
+        <v>547773</v>
       </c>
       <c r="R3" t="n">
-        <v>7152036</v>
+        <v>7152591</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +909,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125338088</v>
+        <v>125338094</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547454</v>
+        <v>547755</v>
       </c>
       <c r="R4" t="n">
-        <v>7152339</v>
+        <v>7152493</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,14 +1016,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125338102</v>
+        <v>125338096</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547134</v>
+        <v>547447</v>
       </c>
       <c r="R5" t="n">
-        <v>7151943</v>
+        <v>7152303</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1081,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125338079</v>
+        <v>125338099</v>
       </c>
       <c r="B6" t="n">
-        <v>80111</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547621</v>
+        <v>547290</v>
       </c>
       <c r="R6" t="n">
-        <v>7152312</v>
+        <v>7152033</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1188,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg naturvårdsträd</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,11 +1233,11 @@
         <v>125338100</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1337,14 +1337,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125338104</v>
+        <v>125338102</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547070</v>
+        <v>547134</v>
       </c>
       <c r="R8" t="n">
-        <v>7151921</v>
+        <v>7151943</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,50 +1444,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125338069</v>
+        <v>125338104</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547781</v>
+        <v>547070</v>
       </c>
       <c r="R9" t="n">
-        <v>7152531</v>
+        <v>7151921</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1519,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,12 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,48 +1551,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125338082</v>
+        <v>125338105</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547586</v>
+        <v>547274</v>
       </c>
       <c r="R10" t="n">
-        <v>7152433</v>
+        <v>7152036</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1634,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,12 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Brandskadad stubbe och låga</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,7 +1640,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1677,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125338071</v>
+        <v>125338082</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,39 +1669,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547313</v>
+        <v>547586</v>
       </c>
       <c r="R11" t="n">
-        <v>7152071</v>
+        <v>7152433</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1752,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,12 +1741,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Brandskadad stubbe och låga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,6 +1755,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1794,10 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125338094</v>
+        <v>125339276</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1785,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547755</v>
+        <v>547306</v>
       </c>
       <c r="R12" t="n">
-        <v>7152493</v>
+        <v>7152046</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1864,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1854,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,32 +1886,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125338099</v>
+        <v>125338079</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>80468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547290</v>
+        <v>547621</v>
       </c>
       <c r="R13" t="n">
-        <v>7152033</v>
+        <v>7152312</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1971,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1981,7 +1966,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg naturvårdsträd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,45 +1998,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125338085</v>
+        <v>125338077</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547489</v>
+        <v>547122</v>
       </c>
       <c r="R14" t="n">
-        <v>7152341</v>
+        <v>7151950</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2078,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,12 +2083,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe</t>
+          <t>Färskt hack vid granbas</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125338096</v>
+        <v>125338069</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,34 +2126,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547447</v>
+        <v>547781</v>
       </c>
       <c r="R15" t="n">
-        <v>7152303</v>
+        <v>7152531</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2200,7 +2200,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,7 +2235,7 @@
         <v>125338070</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125338074</v>
+        <v>125338071</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,37 +2360,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547325</v>
+        <v>547313</v>
       </c>
       <c r="R17" t="n">
-        <v>7152098</v>
+        <v>7152071</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2417,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2427,12 +2434,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,7 +2448,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2460,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125338084</v>
+        <v>126612643</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,37 +2477,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547534</v>
+        <v>547814</v>
       </c>
       <c r="R18" t="n">
-        <v>7152356</v>
+        <v>7152348</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,27 +2536,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125339276</v>
+        <v>126612644</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,37 +2594,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547306</v>
+        <v>547312</v>
       </c>
       <c r="R19" t="n">
-        <v>7152046</v>
+        <v>7152064</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2637,27 +2653,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Brandskadad stubbe</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125338093</v>
+        <v>126612645</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,37 +2711,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547773</v>
+        <v>547244</v>
       </c>
       <c r="R20" t="n">
-        <v>7152591</v>
+        <v>7152003</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2749,22 +2774,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Synobs. 1 Födosökande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,10 +2821,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125338091</v>
+        <v>126612647</v>
       </c>
       <c r="B21" t="n">
-        <v>91250</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,26 +2832,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,13 +2868,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547078</v>
+        <v>547168</v>
       </c>
       <c r="R21" t="n">
-        <v>7151964</v>
+        <v>7151946</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,22 +2898,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Synobs. 2 st födosökande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2883,24 +2927,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2917,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126612645</v>
+        <v>126612648</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,14 +2973,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2961,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547244</v>
+        <v>547122</v>
       </c>
       <c r="R22" t="n">
-        <v>7152003</v>
+        <v>7151913</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,12 +3030,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Synobs. 1 Födosökande</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3062,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126612642</v>
+        <v>126612649</v>
       </c>
       <c r="B23" t="n">
-        <v>91321</v>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3049,34 +3073,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547118</v>
+        <v>547811</v>
       </c>
       <c r="R23" t="n">
-        <v>7151917</v>
+        <v>7152358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,7 +3144,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,12 +3154,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>2 födosökande</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,21 +3170,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3165,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126612643</v>
+        <v>125338074</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,42 +3197,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547814</v>
+        <v>547325</v>
       </c>
       <c r="R24" t="n">
-        <v>7152348</v>
+        <v>7152098</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3235,27 +3254,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,6 +3283,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3282,10 +3302,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126612647</v>
+        <v>125338084</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3293,49 +3313,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547168</v>
+        <v>547534</v>
       </c>
       <c r="R25" t="n">
-        <v>7151946</v>
+        <v>7152356</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3359,27 +3367,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Synobs. 2 st födosökande</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3406,10 +3414,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126612648</v>
+        <v>125338085</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,42 +3425,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547122</v>
+        <v>547489</v>
       </c>
       <c r="R26" t="n">
-        <v>7151913</v>
+        <v>7152341</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,27 +3479,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,10 +3526,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126612649</v>
+        <v>125338088</v>
       </c>
       <c r="B27" t="n">
-        <v>57817</v>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3534,49 +3537,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hålbergsvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547811</v>
+        <v>547454</v>
       </c>
       <c r="R27" t="n">
-        <v>7152358</v>
+        <v>7152339</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3600,27 +3591,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2 födosökande</t>
+          <t>Brandskadad stubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3644,123 +3635,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>126612644</v>
-      </c>
-      <c r="B28" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Hålbergsvägen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>547312</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7152064</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>08:22</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>08:22</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53274-2024 artfynd.xlsx
+++ b/artfynd/A 53274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338093</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338094</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338096</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338099</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338102</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338104</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338105</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338082</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339276</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1995,6 +2055,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338079</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2112,6 +2177,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338077</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2229,6 +2299,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338069</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2346,6 +2421,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338070</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2463,6 +2543,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338071</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2580,6 +2665,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612643</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2697,6 +2787,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612644</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2818,6 +2913,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612645</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2942,6 +3042,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612647</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3059,6 +3164,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612648</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3183,6 +3293,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612649</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3299,6 +3414,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338074</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3411,6 +3531,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338084</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3523,6 +3648,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338085</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3635,8 +3765,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125338088</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>